--- a/cargo_packages_p1-5.xlsx
+++ b/cargo_packages_p1-5.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DPK212614057101</t>
+          <t>YT7642998390994</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -522,17 +522,17 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18749-4-3</t>
+ รถ -</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -542,12 +542,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.0060</t>
+          <t>0.0000</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>144.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -565,11 +565,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>轮胎气门嘴</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -577,7 +573,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>79031204783305</t>
+          <t>DPK212614057101</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -593,7 +589,7 @@
       <c r="E3" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18744-6-15</t>
+ รถ lot18749-4-3</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -613,12 +609,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.0020</t>
+          <t>0.0060</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -628,7 +624,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>39.00฿</t>
+          <t>144.00฿</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -638,7 +634,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>轮胎气门嘴</t>
         </is>
       </c>
     </row>
@@ -648,7 +644,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>435342988112655</t>
+          <t>79031204783305</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -664,17 +660,17 @@
       <c r="E4" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18743-3-34</t>
+ รถ lot18744-6-15</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -684,12 +680,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.0014</t>
+          <t>0.0020</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -699,17 +695,17 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>39.00฿</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>10.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>橡胶垫圈</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -719,7 +715,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>435343890137834</t>
+          <t>435342988112655</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +731,7 @@
       <c r="E5" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18743-7-25</t>
+ รถ lot18743-3-34</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -755,12 +751,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>21.40</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.0080</t>
+          <t>0.0014</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -770,17 +766,17 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>321.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10.00฿</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>扒胎机包胶撬棍</t>
+          <t>橡胶垫圈</t>
         </is>
       </c>
     </row>
@@ -790,7 +786,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>YT7642670434639</t>
+          <t>435343890137834</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -806,7 +802,7 @@
       <c r="E6" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18743-2-8</t>
+ รถ lot18743-7-25</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -826,12 +822,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>21.40</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.0010</t>
+          <t>0.0080</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -841,7 +837,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>12.00฿</t>
+          <t>321.00฿</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -851,7 +847,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>片片</t>
+          <t>扒胎机包胶撬棍</t>
         </is>
       </c>
     </row>
@@ -861,7 +857,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>93015797092</t>
+          <t>YT7642670434639</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -877,12 +873,12 @@
       <c r="E7" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-4-40</t>
+ รถ lot18743-2-8</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -897,12 +893,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>8.60</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.0148</t>
+          <t>0.0010</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -912,7 +908,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>129.00฿</t>
+          <t>12.00฿</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -922,7 +918,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>仪表</t>
+          <t>片片</t>
         </is>
       </c>
     </row>
@@ -932,7 +928,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>YT7642390374765</t>
+          <t>93015797092</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -948,7 +944,7 @@
       <c r="E8" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-4-20</t>
+ รถ lot18735-4-40</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -968,12 +964,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>20.80</t>
+          <t>8.60</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.0598</t>
+          <t>0.0148</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -983,17 +979,17 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>129.00฿</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>358.80฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>打磨机</t>
+          <t>仪表</t>
         </is>
       </c>
     </row>
@@ -1003,7 +999,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>435342255104130</t>
+          <t>YT7642390374765</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1019,7 +1015,7 @@
       <c r="E9" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-43</t>
+ รถ lot18735-4-20</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1039,12 +1035,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.90</t>
+          <t>20.80</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.0172</t>
+          <t>0.0598</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1059,12 +1055,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>103.20฿</t>
+          <t>358.80฿</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>轮毂保护套</t>
+          <t>打磨机</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1070,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>773440312345715</t>
+          <t>435342255104130</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1090,7 +1086,7 @@
       <c r="E10" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-3-78</t>
+ รถ lot18735-43</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1110,12 +1106,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.0013</t>
+          <t>0.0172</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1125,17 +1121,17 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>19.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>103.20฿</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>轮毂保护套</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1141,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>773440291470393</t>
+          <t>773440312345715</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1161,7 +1157,7 @@
       <c r="E11" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-34</t>
+ รถ lot18735-3-78</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1181,12 +1177,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.0029</t>
+          <t>0.0013</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1196,7 +1192,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>48.00฿</t>
+          <t>19.50฿</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1206,7 +1202,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>球阀</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1212,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>435342261175750</t>
+          <t>773440291470393</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1232,7 +1228,7 @@
       <c r="E12" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18736-13</t>
+ รถ lot18735-34</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1242,7 +1238,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1252,12 +1248,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>13.90</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.0137</t>
+          <t>0.0029</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1267,7 +1263,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>208.50฿</t>
+          <t>48.00฿</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1277,7 +1273,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>球阀</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1283,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ZY202461195200</t>
+          <t>435342261175750</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1303,7 +1299,7 @@
       <c r="E13" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18728-7-13</t>
+ รถ lot18736-13</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1323,12 +1319,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>47.40</t>
+          <t>13.90</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.0116</t>
+          <t>0.0137</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1338,7 +1334,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>711.00฿</t>
+          <t>208.50฿</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1358,7 +1354,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>79030687835952</t>
+          <t>ZY202461195200</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1374,7 +1370,7 @@
       <c r="E14" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18728-3-64</t>
+ รถ lot18728-7-13</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1394,12 +1390,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>47.40</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.0030</t>
+          <t>0.0116</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1409,7 +1405,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>64.50฿</t>
+          <t>711.00฿</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1419,7 +1415,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>接头配件</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1425,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LJ20722214#3</t>
+          <t>79030687835952</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1445,17 +1441,17 @@
       <c r="E15" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18726-7-8</t>
+ รถ lot18728-3-64</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1465,12 +1461,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>14.00</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.0171</t>
+          <t>0.0030</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1480,7 +1476,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>210.00฿</t>
+          <t>64.50฿</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1488,7 +1484,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>接头配件</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LJ20722214#2</t>
+          <t>LJ20722214#3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1512,7 +1512,7 @@
       <c r="E16" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18726-7-7</t>
+ รถ lot18726-7-8</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1532,12 +1532,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>11.90</t>
+          <t>14.00</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.0089</t>
+          <t>0.0171</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>178.50฿</t>
+          <t>210.00฿</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>LJ20722214</t>
+          <t>LJ20722214#2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1579,7 +1579,7 @@
       <c r="E17" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18726-7-6</t>
+ รถ lot18726-7-7</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>16.00</t>
+          <t>11.90</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.0144</t>
+          <t>0.0089</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>240.00฿</t>
+          <t>178.50฿</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1622,11 +1622,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>电板套筒配件/3件</t>
-        </is>
-      </c>
+      <c r="N17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1634,7 +1630,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>YT7641966426761</t>
+          <t>LJ20722214</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1650,17 +1646,17 @@
       <c r="E18" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-9-23</t>
+ รถ lot18726-7-6</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1670,12 +1666,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>13.60</t>
+          <t>16.00</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0.0422</t>
+          <t>0.0144</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1685,17 +1681,17 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>240.00฿</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>253.20฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>带表汽车轮胎打气嘴</t>
+          <t>电板套筒配件/3件</t>
         </is>
       </c>
     </row>
@@ -1705,7 +1701,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ZY202471681117#2</t>
+          <t>YT7641966426761</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1721,7 +1717,7 @@
       <c r="E19" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-9-8</t>
+ รถ lot18714-9-23</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1741,12 +1737,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>11.80</t>
+          <t>13.60</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.0832</t>
+          <t>0.0422</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1761,10 +1757,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>499.20฿</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>253.20฿</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>带表汽车轮胎打气嘴</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ZY202471681117</t>
+          <t>ZY202471681117#2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1788,7 +1788,7 @@
       <c r="E20" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-9-7</t>
+ รถ lot18714-9-8</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>7.70</t>
+          <t>11.80</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.0493</t>
+          <t>0.0832</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1828,14 +1828,10 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>295.80฿</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>补胎胶片/2件</t>
-        </is>
-      </c>
+          <t>499.20฿</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1843,7 +1839,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>302285502767#2</t>
+          <t>ZY202471681117</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1859,7 +1855,7 @@
       <c r="E21" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-8-10</t>
+ รถ lot18714-9-7</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1879,12 +1875,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>33.70</t>
+          <t>7.70</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.0145</t>
+          <t>0.0493</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1894,15 +1890,19 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>505.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>295.80฿</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>补胎胶片/2件</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>302285502767</t>
+          <t>302285502767#2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1926,7 +1926,7 @@
       <c r="E22" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-8-9</t>
+ รถ lot18714-8-10</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1946,12 +1946,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>23.40</t>
+          <t>33.70</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.0123</t>
+          <t>0.0145</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>351.00฿</t>
+          <t>505.50฿</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1969,11 +1969,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>扳手</t>
-        </is>
-      </c>
+      <c r="N22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1981,7 +1977,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LJ20716178#2</t>
+          <t>302285502767</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1997,12 +1993,12 @@
       <c r="E23" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18713-6-65</t>
+ รถ lot18714-8-9</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2017,12 +2013,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>19.50</t>
+          <t>23.40</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.0075</t>
+          <t>0.0123</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2032,7 +2028,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>292.50฿</t>
+          <t>351.00฿</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2040,7 +2036,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>扳手</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>LJ20716178</t>
+          <t>LJ20716178#2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2064,7 +2064,7 @@
       <c r="E24" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18713-6-64</t>
+ รถ lot18713-6-65</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>19.60</t>
+          <t>19.50</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>294.00฿</t>
+          <t>292.50฿</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2107,11 +2107,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>配件</t>
-        </is>
-      </c>
+      <c r="N24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2119,7 +2115,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>435338972466812</t>
+          <t>LJ20716178</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2135,7 +2131,7 @@
       <c r="E25" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18710-6-35</t>
+ รถ lot18713-6-64</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2145,7 +2141,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2155,12 +2151,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>13.10</t>
+          <t>19.60</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.0624</t>
+          <t>0.0075</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2170,17 +2166,17 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>294.00฿</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>374.40฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>修补工具</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -2190,7 +2186,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>435334324045675</t>
+          <t>435338972466812</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2200,38 +2196,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>UN-INV260908-00009</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18696-14</t>
+ รถ lot18710-6-35</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>10.80</t>
+          <t>13.10</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.0088</t>
+          <t>0.0624</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2241,17 +2237,17 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>162.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>374.40฿</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>修补工具</t>
         </is>
       </c>
     </row>
@@ -2261,7 +2257,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>YT7641276428798</t>
+          <t>435334324045675</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2277,7 +2273,7 @@
       <c r="E27" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18697-11</t>
+ รถ lot18696-14</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2297,12 +2293,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>9.50</t>
+          <t>10.80</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.0296</t>
+          <t>0.0088</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2312,12 +2308,12 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>162.00฿</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>177.60฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2332,7 +2328,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>79029430531776</t>
+          <t>YT7641276428798</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2342,18 +2338,18 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>UN-INV260907-00015</t>
+          <t>UN-INV260908-00009</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18689-26</t>
+ รถ lot18697-11</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2363,17 +2359,17 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>9.50</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.0135</t>
+          <t>0.0296</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2388,12 +2384,12 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>81.00฿</t>
+          <t>177.60฿</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>卡套</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2399,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>113282578128#2</t>
+          <t>79029430531776</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2419,17 +2415,17 @@
       <c r="E29" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18683-4</t>
+ รถ lot18689-26</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2439,12 +2435,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>38.00</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.1601</t>
+          <t>0.0135</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2459,10 +2455,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>960.60฿</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
+          <t>81.00฿</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>卡套</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>113282578128</t>
+          <t>113282578128#2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2486,7 +2486,7 @@
       <c r="E30" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18683-3</t>
+ รถ lot18683-4</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>27.50</t>
+          <t>38.00</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.1566</t>
+          <t>0.1601</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2526,14 +2526,10 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>939.60฿</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>压条取出器 一票两件破损件</t>
-        </is>
-      </c>
+          <t>960.60฿</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2541,7 +2537,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>82730128600#3</t>
+          <t>113282578128</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2557,12 +2553,12 @@
       <c r="E31" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18678-6-21</t>
+ รถ lot18683-3</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>30/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2577,12 +2573,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>33.00</t>
+          <t>27.50</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.0122</t>
+          <t>0.1566</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2592,15 +2588,19 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>495.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
+          <t>939.60฿</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>压条取出器 一票两件破损件</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>82730128600#2</t>
+          <t>82730128600#3</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2624,7 +2624,7 @@
       <c r="E32" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18678-6-20</t>
+ รถ lot18678-6-21</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>27.60</t>
+          <t>33.00</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.0095</t>
+          <t>0.0122</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>414.00฿</t>
+          <t>495.00฿</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2675,7 +2675,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>82730128600</t>
+          <t>82730128600#2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2691,7 +2691,7 @@
       <c r="E33" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18678-6-19</t>
+ รถ lot18678-6-20</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2711,12 +2711,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>28.10</t>
+          <t>27.60</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.0118</t>
+          <t>0.0095</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>421.50฿</t>
+          <t>414.00฿</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2734,11 +2734,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>五金配件/3件</t>
-        </is>
-      </c>
+      <c r="N33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2746,7 +2742,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>113278387839#3</t>
+          <t>82730128600</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2756,38 +2752,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>UN-INV260903-00023</t>
+          <t>UN-INV260907-00015</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18663-8-3</t>
+ รถ lot18678-6-19</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>30/08/2026</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>25.30</t>
+          <t>28.10</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.0404</t>
+          <t>0.0118</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2797,7 +2793,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>379.50฿</t>
+          <t>421.50฿</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2805,7 +2801,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>五金配件/3件</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>113278387839#2</t>
+          <t>113278387839#3</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2829,7 +2829,7 @@
       <c r="E35" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18663-8-2</t>
+ รถ lot18663-8-3</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>26.10</t>
+          <t>25.30</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.0304</t>
+          <t>0.0404</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2864,7 +2864,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>391.50฿</t>
+          <t>379.50฿</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>113278387839</t>
+          <t>113278387839#2</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2896,7 +2896,7 @@
       <c r="E36" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18663-8-1</t>
+ รถ lot18663-8-2</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>26.10</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.0144</t>
+          <t>0.0304</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>136.50฿</t>
+          <t>391.50฿</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2939,11 +2939,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>配件/3件</t>
-        </is>
-      </c>
+      <c r="N36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2951,7 +2947,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>113276098937#3</t>
+          <t>113278387839</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2961,38 +2957,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>UN-INV260901-00057</t>
+          <t>UN-INV260903-00023</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-45</t>
+ รถ lot18663-8-1</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>17.80</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.0302</t>
+          <t>0.0144</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3002,7 +2998,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>267.00฿</t>
+          <t>136.50฿</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3010,7 +3006,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>配件/3件</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>113276098937#2</t>
+          <t>113276098937#3</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3034,7 +3034,7 @@
       <c r="E38" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-44</t>
+ รถ lot18655-9-45</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>10.90</t>
+          <t>17.80</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.0313</t>
+          <t>0.0302</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3069,12 +3069,12 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>267.00฿</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>187.80฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -3085,7 +3085,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>113276098937</t>
+          <t>113276098937#2</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3101,7 +3101,7 @@
       <c r="E39" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-43</t>
+ รถ lot18655-9-44</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -3121,12 +3121,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>33.60</t>
+          <t>10.90</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.0825</t>
+          <t>0.0313</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -3136,19 +3136,15 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>504.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>补胎胶片+配件/3件</t>
-        </is>
-      </c>
+          <t>187.80฿</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -3156,7 +3152,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ZY202464580877#4</t>
+          <t>113276098937</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3172,7 +3168,7 @@
       <c r="E40" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-17</t>
+ รถ lot18655-9-43</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -3192,12 +3188,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>20.10</t>
+          <t>33.60</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.0466</t>
+          <t>0.0825</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -3207,7 +3203,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>301.50฿</t>
+          <t>504.00฿</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3215,7 +3211,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>补胎胶片+配件/3件</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -3223,7 +3223,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ZY202464580877#7</t>
+          <t>ZY202464580877#4</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3239,7 +3239,7 @@
       <c r="E41" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-16</t>
+ รถ lot18655-9-17</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>16.60</t>
+          <t>20.10</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.0430</t>
+          <t>0.0466</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>301.50฿</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>258.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -3290,7 +3290,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ZY202464580877#2</t>
+          <t>ZY202464580877#7</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3306,7 +3306,7 @@
       <c r="E42" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-15</t>
+ รถ lot18655-9-16</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3326,12 +3326,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>25.10</t>
+          <t>16.60</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.0483</t>
+          <t>0.0430</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3341,12 +3341,12 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>376.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>258.00฿</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -3357,7 +3357,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ZY202464580877#8</t>
+          <t>ZY202464580877#2</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3373,7 +3373,7 @@
       <c r="E43" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-14</t>
+ รถ lot18655-9-15</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>28.90</t>
+          <t>25.10</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.0800</t>
+          <t>0.0483</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>376.50฿</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>480.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -3424,7 +3424,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ZY202464580877#6</t>
+          <t>ZY202464580877#8</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3440,7 +3440,7 @@
       <c r="E44" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-13</t>
+ รถ lot18655-9-14</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3460,12 +3460,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>20.90</t>
+          <t>28.90</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.0534</t>
+          <t>0.0800</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>320.40฿</t>
+          <t>480.00฿</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -3491,7 +3491,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ZY202464580877#5</t>
+          <t>ZY202464580877#6</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3507,7 +3507,7 @@
       <c r="E45" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-12</t>
+ รถ lot18655-9-13</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>26.20</t>
+          <t>20.90</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.0535</t>
+          <t>0.0534</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3542,12 +3542,12 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>393.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>320.40฿</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ZY202464580877</t>
+          <t>ZY202464580877#5</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3574,7 +3574,7 @@
       <c r="E46" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-11</t>
+ รถ lot18655-9-12</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>20.70</t>
+          <t>26.20</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.0531</t>
+          <t>0.0535</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>393.00฿</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>318.60฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
@@ -3625,7 +3625,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ZY202464580877#9</t>
+          <t>ZY202464580877</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3641,7 +3641,7 @@
       <c r="E47" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-10</t>
+ รถ lot18655-9-11</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3661,12 +3661,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>27.70</t>
+          <t>20.70</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>0.0800</t>
+          <t>0.0531</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>480.00฿</t>
+          <t>318.60฿</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -3692,7 +3692,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ZY202464580877#3</t>
+          <t>ZY202464580877#9</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3708,7 +3708,7 @@
       <c r="E48" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-9</t>
+ รถ lot18655-9-10</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3728,12 +3728,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>27.10</t>
+          <t>27.70</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>0.0567</t>
+          <t>0.0800</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3743,19 +3743,15 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>406.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>补胎胶片/9件</t>
-        </is>
-      </c>
+          <t>480.00฿</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3763,7 +3759,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>S71090288685</t>
+          <t>ZY202464580877#3</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3773,38 +3769,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>UN-INV260831-00017</t>
+          <t>UN-INV260901-00057</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18634-7-3</t>
+ รถ lot18655-9-9</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>29/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>12.10</t>
+          <t>27.10</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.0240</t>
+          <t>0.0567</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3814,7 +3810,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>181.50฿</t>
+          <t>406.50฿</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3824,7 +3820,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>补胎胶片/9件</t>
         </is>
       </c>
     </row>
@@ -3834,7 +3830,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>YT7638092409979</t>
+          <t>S71090288685</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3844,38 +3840,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>UN-INV260822-00010</t>
+          <t>UN-INV260831-00017</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18569-7-7</t>
+ รถ lot18634-7-3</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>29/08/2026</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>12.10</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0.0140</t>
+          <t>0.0240</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3885,7 +3881,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>225.00฿</t>
+          <t>181.50฿</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3905,7 +3901,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>435308000517585</t>
+          <t>YT7638092409979</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3921,32 +3917,32 @@
       <c r="E51" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18550-6-11</t>
+ รถ lot18569-7-7</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>0.0032</t>
+          <t>0.0140</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3956,7 +3952,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>54.00฿</t>
+          <t>225.00฿</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -3966,7 +3962,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>气门嘴</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -3976,7 +3972,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>710094401487</t>
+          <t>435308000517585</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3992,17 +3988,17 @@
       <c r="E52" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18544-8-14</t>
+ รถ lot18550-6-11</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4012,32 +4008,32 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>107.10</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>0.4536</t>
+          <t>0.0032</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>54.00฿</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2,721.60฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>空的高压充气罐/一票10件，仓库实收到9件，已确认收到的9件先发</t>
+          <t>气门嘴</t>
         </is>
       </c>
     </row>
@@ -4047,7 +4043,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>773435675083665</t>
+          <t>710094401487</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4057,58 +4053,58 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>UN-INV260815-00046</t>
+          <t>UN-INV260822-00010</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18526-6-17</t>
+ รถ lot18544-8-14</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>13.10</t>
+          <t>107.10</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>0.0214</t>
+          <t>0.4536</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>196.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2,721.60฿</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>补胎工具</t>
+          <t>空的高压充气罐/一票10件，仓库实收到9件，已确认收到的9件先发</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4114,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>YT7637032206975</t>
+          <t>773435675083665</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4128,38 +4124,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>UN-INV260819-00010</t>
+          <t>UN-INV260815-00046</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>มอก.
- รถ lot18523-6-30</t>
+          <t>ธรรมดา
+ รถ lot18526-6-17</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>13.10</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>0.0316</t>
+          <t>0.0214</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -4169,17 +4165,17 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>196.50฿</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>214.88฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>气动模具研磨机+配件</t>
+          <t>补胎工具</t>
         </is>
       </c>
     </row>
@@ -4189,7 +4185,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ZY202466648481#5</t>
+          <t>YT7637032206975</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4199,13 +4195,13 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>UN-INV260815-00046</t>
+          <t>UN-INV260819-00010</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>ธรรมดา
- รถ lot18519-6-17</t>
+          <t>มอก.
+ รถ lot18523-6-30</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -4220,17 +4216,17 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>16.10</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>0.0493</t>
+          <t>0.0316</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -4245,10 +4241,14 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>295.80฿</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
+          <t>214.88฿</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>气动模具研磨机+配件</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ZY202466648481#4</t>
+          <t>ZY202466648481#5</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4272,7 +4272,7 @@
       <c r="E56" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18519-6-16</t>
+ รถ lot18519-6-17</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>20.50</t>
+          <t>16.10</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>0.0656</t>
+          <t>0.0493</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>393.60฿</t>
+          <t>295.80฿</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -4323,7 +4323,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ZY202466648481#3</t>
+          <t>ZY202466648481#4</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4339,7 +4339,7 @@
       <c r="E57" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18519-6-15</t>
+ รถ lot18519-6-16</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -4359,12 +4359,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>15.70</t>
+          <t>20.50</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>0.0508</t>
+          <t>0.0656</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -4379,7 +4379,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>304.80฿</t>
+          <t>393.60฿</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
@@ -4390,7 +4390,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ZY202466648481#2</t>
+          <t>ZY202466648481#3</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4406,7 +4406,7 @@
       <c r="E58" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18519-6-14</t>
+ รถ lot18519-6-15</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -4426,12 +4426,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>20.20</t>
+          <t>15.70</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>0.0660</t>
+          <t>0.0508</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>396.00฿</t>
+          <t>304.80฿</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ZY202466648481</t>
+          <t>ZY202466648481#2</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4473,7 +4473,7 @@
       <c r="E59" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18519-6-13</t>
+ รถ lot18519-6-14</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -4493,12 +4493,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>15.80</t>
+          <t>20.20</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>0.0522</t>
+          <t>0.0660</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4513,14 +4513,10 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>313.20฿</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>补胎胶条/5件</t>
-        </is>
-      </c>
+          <t>396.00฿</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -4528,7 +4524,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>113204676267#2</t>
+          <t>ZY202466648481</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4544,32 +4540,32 @@
       <c r="E60" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18518-5-3</t>
+ รถ lot18519-6-13</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>15/08/2026</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>24.60</t>
+          <t>15.80</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>0.0608</t>
+          <t>0.0522</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4579,15 +4575,19 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>369.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
+          <t>313.20฿</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>补胎胶条/5件</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -4595,7 +4595,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>113204676267</t>
+          <t>113204676267#2</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4611,7 +4611,7 @@
       <c r="E61" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18518-5-2</t>
+ รถ lot18518-5-3</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -4631,12 +4631,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>25.00</t>
+          <t>24.60</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>0.0566</t>
+          <t>0.0608</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>375.00฿</t>
+          <t>369.00฿</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -4654,11 +4654,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>真空胎冷补胶片</t>
-        </is>
-      </c>
+      <c r="N61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -4666,7 +4662,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>910061892464#2</t>
+          <t>113204676267</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4682,32 +4678,32 @@
       <c r="E62" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18505-5-23</t>
+ รถ lot18518-5-2</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>30.40</t>
+          <t>25.00</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>0.0523</t>
+          <t>0.0566</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4717,7 +4713,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>456.00฿</t>
+          <t>375.00฿</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -4725,7 +4721,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>真空胎冷补胶片</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>910061892464</t>
+          <t>910061892464#2</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4749,7 +4749,7 @@
       <c r="E63" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18505-5-22</t>
+ รถ lot18505-5-23</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -4769,12 +4769,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>15.90</t>
+          <t>30.40</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>0.0353</t>
+          <t>0.0523</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -4784,7 +4784,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>238.50฿</t>
+          <t>456.00฿</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -4792,11 +4792,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>记号蜡笔</t>
-        </is>
-      </c>
+      <c r="N63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -4804,7 +4800,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>773434709817985</t>
+          <t>910061892464</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4814,38 +4810,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>UN-INV260819-00010</t>
+          <t>UN-INV260815-00046</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18535-8</t>
+ รถ lot18505-5-22</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>15.90</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>0.0184</t>
+          <t>0.0353</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4855,17 +4851,17 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>238.50฿</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>110.40฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>锅具 二次包装货物变形</t>
+          <t>记号蜡笔</t>
         </is>
       </c>
     </row>
@@ -4875,7 +4871,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>435295775627304</t>
+          <t>773434709817985</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4885,38 +4881,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>UN-INV260811-00012</t>
+          <t>UN-INV260819-00010</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18492-2</t>
+ รถ lot18535-8</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>5.30</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>0.0090</t>
+          <t>0.0184</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4926,17 +4922,17 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>79.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>110.40฿</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>配件 破损件</t>
+          <t>锅具 二次包装货物变形</t>
         </is>
       </c>
     </row>
@@ -4946,7 +4942,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>YT7636332367470</t>
+          <t>435295775627304</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4962,7 +4958,7 @@
       <c r="E66" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18487-2-27</t>
+ รถ lot18492-2</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -4982,12 +4978,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>5.30</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>0.0004</t>
+          <t>0.0090</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -4997,17 +4993,17 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>79.50฿</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>10.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>立牌</t>
+          <t>配件 破损件</t>
         </is>
       </c>
     </row>
@@ -5017,7 +5013,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>S35386280517#2</t>
+          <t>YT7636332367470</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -5033,32 +5029,32 @@
       <c r="E67" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18475-24</t>
+ รถ lot18487-2-27</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>8.80</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>0.0045</t>
+          <t>0.0004</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -5068,15 +5064,19 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>132.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
+          <t>10.00฿</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>立牌</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -5084,7 +5084,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>S35386280517</t>
+          <t>S35386280517#2</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -5100,7 +5100,7 @@
       <c r="E68" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18475-23</t>
+ รถ lot18475-24</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -5120,22 +5120,22 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>103.50</t>
+          <t>8.80</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>0.2236</t>
+          <t>0.0045</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>1,552.50฿</t>
+          <t>132.00฿</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -5143,11 +5143,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>气门嘴 顺心捷达，一票16件</t>
-        </is>
-      </c>
+      <c r="N68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -5155,7 +5151,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>YT7635787693833</t>
+          <t>S35386280517</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -5171,7 +5167,7 @@
       <c r="E69" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18473-6-41</t>
+ รถ lot18475-23</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -5186,37 +5182,37 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>13.80</t>
+          <t>103.50</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>0.0432</t>
+          <t>0.2236</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1,552.50฿</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>259.20฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>气压表/面单没有代码</t>
+          <t>气门嘴 顺心捷达，一票16件</t>
         </is>
       </c>
     </row>
@@ -5226,7 +5222,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ZY202465806614</t>
+          <t>YT7635787693833</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -5236,38 +5232,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>UN-INV260807-00009</t>
+          <t>UN-INV260811-00012</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>มอก.
- รถ lot18466-5-51</t>
+          <t>ธรรมดา
+ รถ lot18473-6-41</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>11.30</t>
+          <t>13.80</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>0.0655</t>
+          <t>0.0432</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -5282,12 +5278,12 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>445.40฿</t>
+          <t>259.20฿</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>电子数显胎压枪</t>
+          <t>气压表/面单没有代码</t>
         </is>
       </c>
     </row>
@@ -5297,7 +5293,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>113177184579#7</t>
+          <t>ZY202465806614</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -5312,18 +5308,18 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>ธรรมดา
- รถ lot18463-17</t>
+          <t>มอก.
+ รถ lot18466-5-51</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5333,12 +5329,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>9.70</t>
+          <t>11.30</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>0.0305</t>
+          <t>0.0655</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -5353,10 +5349,14 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>183.00฿</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
+          <t>445.40฿</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>电子数显胎压枪</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -5364,7 +5364,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>113177184579#5</t>
+          <t>113177184579#7</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -5380,7 +5380,7 @@
       <c r="E72" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-16</t>
+ รถ lot18463-17</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>9.70</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>0.0137</t>
+          <t>0.0305</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -5415,12 +5415,12 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>225.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>183.00฿</t>
         </is>
       </c>
       <c r="N72" t="inlineStr"/>
@@ -5431,7 +5431,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>113177184579#4</t>
+          <t>113177184579#5</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -5447,7 +5447,7 @@
       <c r="E73" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-15</t>
+ รถ lot18463-16</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>7.30</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>0.0235</t>
+          <t>0.0137</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>225.00฿</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>141.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N73" t="inlineStr"/>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>113177184579#3</t>
+          <t>113177184579#4</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5514,7 +5514,7 @@
       <c r="E74" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-14</t>
+ รถ lot18463-15</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -5534,12 +5534,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>11.90</t>
+          <t>7.30</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>0.0302</t>
+          <t>0.0235</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>181.20฿</t>
+          <t>141.00฿</t>
         </is>
       </c>
       <c r="N74" t="inlineStr"/>
@@ -5565,7 +5565,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>113177184579#6</t>
+          <t>113177184579#3</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5581,7 +5581,7 @@
       <c r="E75" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-13</t>
+ รถ lot18463-14</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -5601,12 +5601,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>26.10</t>
+          <t>11.90</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>0.0673</t>
+          <t>0.0302</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>403.80฿</t>
+          <t>181.20฿</t>
         </is>
       </c>
       <c r="N75" t="inlineStr"/>
@@ -5632,7 +5632,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>435289604798626</t>
+          <t>113177184579#6</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5648,7 +5648,7 @@
       <c r="E76" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18462-6-6</t>
+ รถ lot18463-13</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -5658,7 +5658,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5668,12 +5668,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>26.10</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>0.0090</t>
+          <t>0.0673</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -5683,19 +5683,15 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>144.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>螺丝配件</t>
-        </is>
-      </c>
+          <t>403.80฿</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -5703,7 +5699,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>113177184579#2</t>
+          <t>435289604798626</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5719,7 +5715,7 @@
       <c r="E77" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-12</t>
+ รถ lot18462-6-6</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -5729,7 +5725,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5739,12 +5735,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>5.30</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>0.0635</t>
+          <t>0.0090</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5754,15 +5750,19 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>144.00฿</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>381.00฿</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>螺丝配件</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -5770,7 +5770,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>113177184579</t>
+          <t>113177184579#2</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5786,7 +5786,7 @@
       <c r="E78" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-11</t>
+ รถ lot18463-12</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>13.30</t>
+          <t>5.30</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>0.1176</t>
+          <t>0.0635</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -5826,14 +5826,10 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>705.60฿</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t>蘑菇钉补胎贴</t>
-        </is>
-      </c>
+          <t>381.00฿</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -5841,7 +5837,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>435289604798722</t>
+          <t>113177184579</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5857,7 +5853,7 @@
       <c r="E79" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18462-3</t>
+ รถ lot18463-11</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -5867,7 +5863,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5877,12 +5873,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>13.30</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>0.0029</t>
+          <t>0.1176</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -5892,17 +5888,17 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>64.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>705.60฿</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>气门嘴</t>
+          <t>蘑菇钉补胎贴</t>
         </is>
       </c>
     </row>
@@ -5912,7 +5908,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>ZY202471573119#2</t>
+          <t>435289604798722</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5928,7 +5924,7 @@
       <c r="E80" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-6</t>
+ รถ lot18462-3</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -5938,7 +5934,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5948,12 +5944,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>8.70</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>0.0441</t>
+          <t>0.0029</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -5963,15 +5959,19 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>64.50฿</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>264.60฿</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>气门嘴</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -5979,7 +5979,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ZY202471573119</t>
+          <t>ZY202471573119#2</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5995,7 +5995,7 @@
       <c r="E81" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-5</t>
+ รถ lot18463-6</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>11.90</t>
+          <t>8.70</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>0.0832</t>
+          <t>0.0441</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -6035,14 +6035,10 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>499.20฿</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>蘑菇钉补胎</t>
-        </is>
-      </c>
+          <t>264.60฿</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -6050,7 +6046,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>YT7635427281240</t>
+          <t>ZY202471573119</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -6066,7 +6062,7 @@
       <c r="E82" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18458-21</t>
+ รถ lot18463-5</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -6086,12 +6082,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>11.90</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>0.0117</t>
+          <t>0.0832</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -6106,12 +6102,12 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>70.20฿</t>
+          <t>499.20฿</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>气阀</t>
+          <t>蘑菇钉补胎</t>
         </is>
       </c>
     </row>
@@ -6121,7 +6117,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>79021262374216</t>
+          <t>YT7635427281240</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -6131,38 +6127,38 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>UN-INV260804-00019</t>
+          <t>UN-INV260807-00009</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18435-5-73</t>
+ รถ lot18458-21</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>12.20</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>0.0352</t>
+          <t>0.0117</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -6177,12 +6173,12 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>211.20฿</t>
+          <t>70.20฿</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>加长弯头</t>
+          <t>气阀</t>
         </is>
       </c>
     </row>
@@ -6192,7 +6188,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>113162219964#3</t>
+          <t>79021262374216</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -6208,17 +6204,17 @@
       <c r="E84" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18434-9-28</t>
+ รถ lot18435-5-73</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -6228,12 +6224,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>18.70</t>
+          <t>12.20</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>0.0443</t>
+          <t>0.0352</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -6243,15 +6239,19 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>280.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr"/>
+          <t>211.20฿</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>加长弯头</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -6259,7 +6259,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>113162219964#2</t>
+          <t>113162219964#3</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -6275,7 +6275,7 @@
       <c r="E85" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18434-9-27</t>
+ รถ lot18434-9-28</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>22.90</t>
+          <t>18.70</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>0.0522</t>
+          <t>0.0443</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -6310,7 +6310,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>343.50฿</t>
+          <t>280.50฿</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>113162219964</t>
+          <t>113162219964#2</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -6342,7 +6342,7 @@
       <c r="E86" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18434-9-26</t>
+ รถ lot18434-9-27</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -6362,12 +6362,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>25.60</t>
+          <t>22.90</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>0.0574</t>
+          <t>0.0522</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -6377,7 +6377,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>384.00฿</t>
+          <t>343.50฿</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -6385,11 +6385,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>补胎胶片/3件</t>
-        </is>
-      </c>
+      <c r="N86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -6397,7 +6393,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>113158800045#2</t>
+          <t>113162219964</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -6413,32 +6409,32 @@
       <c r="E87" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18427-7-3</t>
+ รถ lot18434-9-26</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>26/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>26/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>26.30</t>
+          <t>25.60</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>0.0377</t>
+          <t>0.0574</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -6448,7 +6444,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>394.50฿</t>
+          <t>384.00฿</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -6456,7 +6452,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N87" t="inlineStr"/>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>补胎胶片/3件</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>113158800045</t>
+          <t>113158800045#2</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -6480,7 +6480,7 @@
       <c r="E88" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18427-7-2</t>
+ รถ lot18427-7-3</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -6500,12 +6500,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>26.50</t>
+          <t>26.30</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>0.0379</t>
+          <t>0.0377</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -6515,7 +6515,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>397.50฿</t>
+          <t>394.50฿</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -6523,11 +6523,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N88" t="inlineStr">
-        <is>
-          <t>塑料配件/2件</t>
-        </is>
-      </c>
+      <c r="N88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -6535,7 +6531,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>YT2550516723148</t>
+          <t>113158800045</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -6551,32 +6547,32 @@
       <c r="E89" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18398-3-10</t>
+ รถ lot18427-7-2</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>26/07/2026</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>26/07/2026</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>26.50</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>0.0127</t>
+          <t>0.0379</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -6586,17 +6582,17 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>397.50฿</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>76.20฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>硅胶风管</t>
+          <t>塑料配件/2件</t>
         </is>
       </c>
     </row>
@@ -6606,7 +6602,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>ZY202467269952#4</t>
+          <t>YT2550516723148</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -6616,38 +6612,38 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>UN-INV260724-00013</t>
+          <t>UN-INV260804-00019</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18314-8-30</t>
+ รถ lot18398-3-10</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>11/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>12/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>15.50</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>0.0492</t>
+          <t>0.0127</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -6662,10 +6658,14 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>295.20฿</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr"/>
+          <t>76.20฿</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>硅胶风管</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -6673,7 +6673,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>ZY202467269952#3</t>
+          <t>ZY202467269952#4</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6689,7 +6689,7 @@
       <c r="E91" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18314-8-29</t>
+ รถ lot18314-8-30</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -6709,12 +6709,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>12.50</t>
+          <t>15.50</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>0.0300</t>
+          <t>0.0492</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>187.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>295.20฿</t>
         </is>
       </c>
       <c r="N91" t="inlineStr"/>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>ZY202467269952#2</t>
+          <t>ZY202467269952#3</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6756,7 +6756,7 @@
       <c r="E92" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18314-8-28</t>
+ รถ lot18314-8-29</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>15.50</t>
+          <t>12.50</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>0.0508</t>
+          <t>0.0300</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -6791,12 +6791,12 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>187.50฿</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>304.80฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N92" t="inlineStr"/>
@@ -6807,7 +6807,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>ZY202467269952</t>
+          <t>ZY202467269952#2</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6823,7 +6823,7 @@
       <c r="E93" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18314-8-27</t>
+ รถ lot18314-8-28</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -6843,12 +6843,12 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>10.50</t>
+          <t>15.50</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>0.0355</t>
+          <t>0.0508</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -6863,14 +6863,10 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>213.00฿</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr">
-        <is>
-          <t>补胎胶片/4件</t>
-        </is>
-      </c>
+          <t>304.80฿</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -6878,7 +6874,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>773431041004504</t>
+          <t>ZY202467269952</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6894,7 +6890,7 @@
       <c r="E94" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18314-5-13</t>
+ รถ lot18314-8-27</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -6914,12 +6910,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>10.50</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>0.0044</t>
+          <t>0.0355</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -6934,12 +6930,12 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>26.40฿</t>
+          <t>213.00฿</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>门底条</t>
+          <t>补胎胶片/4件</t>
         </is>
       </c>
     </row>
@@ -6949,7 +6945,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>ZY202467269844#2</t>
+          <t>773431041004504</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6959,38 +6955,38 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>UN-INV260717-00013</t>
+          <t>UN-INV260724-00013</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18288-8-41</t>
+ รถ lot18314-5-13</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>11/07/2026</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>12/07/2026</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>21.00</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>0.0660</t>
+          <t>0.0044</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -7005,10 +7001,14 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>396.00฿</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr"/>
+          <t>26.40฿</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>门底条</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -7016,7 +7016,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>ZY202467269844#5</t>
+          <t>ZY202467269844#2</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -7032,7 +7032,7 @@
       <c r="E96" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18288-8-40</t>
+ รถ lot18288-8-41</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -7052,12 +7052,12 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>27.90</t>
+          <t>21.00</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>0.0800</t>
+          <t>0.0660</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -7072,7 +7072,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>480.00฿</t>
+          <t>396.00฿</t>
         </is>
       </c>
       <c r="N96" t="inlineStr"/>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>ZY202467269844#3</t>
+          <t>ZY202467269844#5</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -7099,7 +7099,7 @@
       <c r="E97" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18288-8-39</t>
+ รถ lot18288-8-40</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>15.60</t>
+          <t>27.90</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>0.0496</t>
+          <t>0.0800</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -7139,7 +7139,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>297.60฿</t>
+          <t>480.00฿</t>
         </is>
       </c>
       <c r="N97" t="inlineStr"/>
@@ -7150,7 +7150,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ZY202467269844#4</t>
+          <t>ZY202467269844#3</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -7166,7 +7166,7 @@
       <c r="E98" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18288-8-38</t>
+ รถ lot18288-8-39</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -7186,12 +7186,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>16.00</t>
+          <t>15.60</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>0.0504</t>
+          <t>0.0496</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -7206,7 +7206,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>302.40฿</t>
+          <t>297.60฿</t>
         </is>
       </c>
       <c r="N98" t="inlineStr"/>
@@ -7217,7 +7217,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ZY202467269844#6</t>
+          <t>ZY202467269844#4</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -7233,7 +7233,7 @@
       <c r="E99" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18288-8-37</t>
+ รถ lot18288-8-38</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>29.00</t>
+          <t>16.00</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>0.0816</t>
+          <t>0.0504</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -7273,7 +7273,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>489.60฿</t>
+          <t>302.40฿</t>
         </is>
       </c>
       <c r="N99" t="inlineStr"/>
@@ -7284,7 +7284,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>ZY202467269844#7</t>
+          <t>ZY202467269844#6</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -7300,7 +7300,7 @@
       <c r="E100" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18288-8-36</t>
+ รถ lot18288-8-37</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -7320,12 +7320,12 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>15.80</t>
+          <t>29.00</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>0.0519</t>
+          <t>0.0816</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -7340,14 +7340,10 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>311.40฿</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr">
-        <is>
-          <t>补胎胶片/一票7件，已确认6件发陆运1件发海运</t>
-        </is>
-      </c>
+          <t>489.60฿</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -7355,7 +7351,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>ZY202467269844</t>
+          <t>ZY202467269844#7</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -7365,38 +7361,38 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>UN-INV260804-00019</t>
+          <t>UN-INV260717-00013</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>อย.
- เรือ 18350-91</t>
+          <t>ธรรมดา
+ รถ lot18288-8-36</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>19.80</t>
+          <t>15.80</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>0.0648</t>
+          <t>0.0519</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -7406,17 +7402,17 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>396.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>311.40฿</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>清洗剂/一票7件，已确认6件发陆运1件发海运</t>
+          <t>补胎胶片/一票7件，已确认6件发陆运1件发海运</t>
         </is>
       </c>
     </row>

--- a/cargo_packages_p1-5.xlsx
+++ b/cargo_packages_p1-5.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>YT7642998390994</t>
+          <t>ZY202472578299</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -522,12 +522,12 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ -</t>
+ รถ lot18758-7-43</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -542,17 +542,17 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>47.40</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.1603</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -562,10 +562,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>961.20฿</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>补胎贴，3件</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -573,7 +577,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DPK212614057101</t>
+          <t>773440822655698</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -589,17 +593,17 @@
       <c r="E3" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18749-4-3</t>
+ รถ lot18758-4-31</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -609,12 +613,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.0060</t>
+          <t>0.0022</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -624,7 +628,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>144.00฿</t>
+          <t>18.00฿</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -634,7 +638,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>轮胎气门嘴</t>
+          <t>钻头</t>
         </is>
       </c>
     </row>
@@ -644,7 +648,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>79031204783305</t>
+          <t>YT7642998390994</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -660,17 +664,17 @@
       <c r="E4" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18744-6-15</t>
+ รถ -</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -680,12 +684,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.0020</t>
+          <t>0.0000</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -695,7 +699,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>39.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -703,11 +707,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>配件</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -715,7 +715,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>435342988112655</t>
+          <t>DPK212614057101</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -731,17 +731,17 @@
       <c r="E5" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18743-3-34</t>
+ รถ lot18749-4-3</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -751,12 +751,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.0014</t>
+          <t>0.0060</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -766,17 +766,17 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>144.00฿</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>10.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>橡胶垫圈</t>
+          <t>轮胎气门嘴</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>435343890137834</t>
+          <t>79031204783305</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -802,17 +802,17 @@
       <c r="E6" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18743-7-25</t>
+ รถ lot18744-6-15</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -822,12 +822,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>21.40</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.0080</t>
+          <t>0.0020</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>321.00฿</t>
+          <t>39.00฿</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>扒胎机包胶撬棍</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>YT7642670434639</t>
+          <t>435342988112655</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -873,7 +873,7 @@
       <c r="E7" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18743-2-8</t>
+ รถ lot18743-3-34</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.0010</t>
+          <t>0.0014</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -908,17 +908,17 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>12.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10.00฿</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>片片</t>
+          <t>橡胶垫圈</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>93015797092</t>
+          <t>435343890137834</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -944,12 +944,12 @@
       <c r="E8" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-4-40</t>
+ รถ lot18743-7-25</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -964,12 +964,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>8.60</t>
+          <t>21.40</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.0148</t>
+          <t>0.0080</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>129.00฿</t>
+          <t>321.00฿</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>仪表</t>
+          <t>扒胎机包胶撬棍</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>YT7642390374765</t>
+          <t>YT7642670434639</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1015,12 +1015,12 @@
       <c r="E9" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-4-20</t>
+ รถ lot18743-2-8</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1035,12 +1035,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>20.80</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.0598</t>
+          <t>0.0010</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1050,17 +1050,17 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12.00฿</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>358.80฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>打磨机</t>
+          <t>片片</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>435342255104130</t>
+          <t>93015797092</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1086,7 +1086,7 @@
       <c r="E10" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-43</t>
+ รถ lot18735-4-40</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.90</t>
+          <t>8.60</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.0172</t>
+          <t>0.0148</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1121,17 +1121,17 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>129.00฿</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>103.20฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>轮毂保护套</t>
+          <t>仪表</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>773440312345715</t>
+          <t>YT7642390374765</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1157,7 +1157,7 @@
       <c r="E11" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-3-78</t>
+ รถ lot18735-4-20</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1177,12 +1177,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>20.80</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.0013</t>
+          <t>0.0598</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1192,17 +1192,17 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>19.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>358.80฿</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>打磨机</t>
         </is>
       </c>
     </row>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>773440291470393</t>
+          <t>435342255104130</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1228,7 +1228,7 @@
       <c r="E12" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18735-34</t>
+ รถ lot18735-43</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1248,12 +1248,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.0029</t>
+          <t>0.0172</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1263,17 +1263,17 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>48.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>103.20฿</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>球阀</t>
+          <t>轮毂保护套</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>435342261175750</t>
+          <t>773440312345715</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1299,7 +1299,7 @@
       <c r="E13" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18736-13</t>
+ รถ lot18735-3-78</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>13.90</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.0137</t>
+          <t>0.0013</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>208.50฿</t>
+          <t>19.50฿</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ZY202461195200</t>
+          <t>773440291470393</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1370,7 +1370,7 @@
       <c r="E14" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18728-7-13</t>
+ รถ lot18735-34</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1380,7 +1380,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1390,12 +1390,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>47.40</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.0116</t>
+          <t>0.0029</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>711.00฿</t>
+          <t>48.00฿</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1415,7 +1415,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>球阀</t>
         </is>
       </c>
     </row>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>79030687835952</t>
+          <t>435342261175750</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1441,7 +1441,7 @@
       <c r="E15" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18728-3-64</t>
+ รถ lot18736-13</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1461,12 +1461,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>13.90</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.0030</t>
+          <t>0.0137</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>64.50฿</t>
+          <t>208.50฿</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>接头配件</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LJ20722214#3</t>
+          <t>ZY202461195200</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1512,17 +1512,17 @@
       <c r="E16" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18726-7-8</t>
+ รถ lot18728-7-13</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1532,12 +1532,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>14.00</t>
+          <t>47.40</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.0171</t>
+          <t>0.0116</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>210.00฿</t>
+          <t>711.00฿</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1555,7 +1555,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>配件</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1563,7 +1567,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>LJ20722214#2</t>
+          <t>79030687835952</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1579,17 +1583,17 @@
       <c r="E17" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18726-7-7</t>
+ รถ lot18728-3-64</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1599,12 +1603,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>11.90</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.0089</t>
+          <t>0.0030</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1614,7 +1618,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>178.50฿</t>
+          <t>64.50฿</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1622,7 +1626,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>接头配件</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1630,7 +1638,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LJ20722214</t>
+          <t>LJ20722214#3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1646,7 +1654,7 @@
       <c r="E18" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18726-7-6</t>
+ รถ lot18726-7-8</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1666,12 +1674,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>16.00</t>
+          <t>14.00</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0.0144</t>
+          <t>0.0171</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1681,7 +1689,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>240.00฿</t>
+          <t>210.00฿</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1689,11 +1697,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>电板套筒配件/3件</t>
-        </is>
-      </c>
+      <c r="N18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1701,7 +1705,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>YT7641966426761</t>
+          <t>LJ20722214#2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1717,17 +1721,17 @@
       <c r="E19" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-9-23</t>
+ รถ lot18726-7-7</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1737,12 +1741,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>13.60</t>
+          <t>11.90</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.0422</t>
+          <t>0.0089</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1752,19 +1756,15 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>178.50฿</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>253.20฿</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>带表汽车轮胎打气嘴</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ZY202471681117#2</t>
+          <t>LJ20722214</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1788,17 +1788,17 @@
       <c r="E20" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-9-8</t>
+ รถ lot18726-7-6</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>11.80</t>
+          <t>16.00</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.0832</t>
+          <t>0.0144</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1823,15 +1823,19 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>240.00฿</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>499.20฿</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>电板套筒配件/3件</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1839,7 +1843,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ZY202471681117</t>
+          <t>YT7641966426761</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1855,7 +1859,7 @@
       <c r="E21" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-9-7</t>
+ รถ lot18714-9-23</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1875,12 +1879,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>7.70</t>
+          <t>13.60</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.0493</t>
+          <t>0.0422</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1895,12 +1899,12 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>295.80฿</t>
+          <t>253.20฿</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>补胎胶片/2件</t>
+          <t>带表汽车轮胎打气嘴</t>
         </is>
       </c>
     </row>
@@ -1910,7 +1914,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>302285502767#2</t>
+          <t>ZY202471681117#2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1926,7 +1930,7 @@
       <c r="E22" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-8-10</t>
+ รถ lot18714-9-8</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1946,12 +1950,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>33.70</t>
+          <t>11.80</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.0145</t>
+          <t>0.0832</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1961,12 +1965,12 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>505.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>499.20฿</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -1977,7 +1981,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>302285502767</t>
+          <t>ZY202471681117</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1993,7 +1997,7 @@
       <c r="E23" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18714-8-9</t>
+ รถ lot18714-9-7</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2013,12 +2017,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>23.40</t>
+          <t>7.70</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.0123</t>
+          <t>0.0493</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2028,17 +2032,17 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>351.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>295.80฿</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>扳手</t>
+          <t>补胎胶片/2件</t>
         </is>
       </c>
     </row>
@@ -2048,7 +2052,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>LJ20716178#2</t>
+          <t>302285502767#2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2064,12 +2068,12 @@
       <c r="E24" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18713-6-65</t>
+ รถ lot18714-8-10</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2084,12 +2088,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>19.50</t>
+          <t>33.70</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.0075</t>
+          <t>0.0145</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2099,7 +2103,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>292.50฿</t>
+          <t>505.50฿</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2115,7 +2119,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>LJ20716178</t>
+          <t>302285502767</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2131,12 +2135,12 @@
       <c r="E25" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18713-6-64</t>
+ รถ lot18714-8-9</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2151,12 +2155,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>19.60</t>
+          <t>23.40</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.0075</t>
+          <t>0.0123</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2166,7 +2170,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>294.00฿</t>
+          <t>351.00฿</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2176,7 +2180,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>扳手</t>
         </is>
       </c>
     </row>
@@ -2186,7 +2190,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>435338972466812</t>
+          <t>LJ20716178#2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2202,7 +2206,7 @@
       <c r="E26" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18710-6-35</t>
+ รถ lot18713-6-65</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2212,22 +2216,22 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>13.10</t>
+          <t>19.50</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.0624</t>
+          <t>0.0075</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2237,19 +2241,15 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>292.50฿</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>374.40฿</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>修补工具</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>435334324045675</t>
+          <t>LJ20716178</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2267,38 +2267,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>UN-INV260908-00009</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18696-14</t>
+ รถ lot18713-6-64</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>10.80</t>
+          <t>19.60</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.0088</t>
+          <t>0.0075</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>162.00฿</t>
+          <t>294.00฿</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2328,7 +2328,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>YT7641276428798</t>
+          <t>435338972466812</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2338,38 +2338,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>UN-INV260908-00009</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18697-11</t>
+ รถ lot18710-6-35</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>9.50</t>
+          <t>13.10</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.0296</t>
+          <t>0.0624</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>177.60฿</t>
+          <t>374.40฿</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>修补工具</t>
         </is>
       </c>
     </row>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>79029430531776</t>
+          <t>435334324045675</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2409,18 +2409,18 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>UN-INV260907-00015</t>
+          <t>UN-INV260908-00009</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18689-26</t>
+ รถ lot18696-14</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2430,17 +2430,17 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>10.80</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.0135</t>
+          <t>0.0088</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2450,17 +2450,17 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>162.00฿</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>81.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>卡套</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>113282578128#2</t>
+          <t>YT7641276428798</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2480,38 +2480,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>UN-INV260907-00015</t>
+          <t>UN-INV260908-00009</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18683-4</t>
+ รถ lot18697-11</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>38.00</t>
+          <t>9.50</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.1601</t>
+          <t>0.0296</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2526,10 +2526,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>960.60฿</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
+          <t>177.60฿</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>配件</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2537,7 +2541,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>113282578128</t>
+          <t>79029430531776</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2553,17 +2557,17 @@
       <c r="E31" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18683-3</t>
+ รถ lot18689-26</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2573,12 +2577,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>27.50</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.1566</t>
+          <t>0.0135</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2593,12 +2597,12 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>939.60฿</t>
+          <t>81.00฿</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>压条取出器 一票两件破损件</t>
+          <t>卡套</t>
         </is>
       </c>
     </row>
@@ -2608,7 +2612,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>82730128600#3</t>
+          <t>113282578128#2</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2624,12 +2628,12 @@
       <c r="E32" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18678-6-21</t>
+ รถ lot18683-4</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>30/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2644,12 +2648,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>33.00</t>
+          <t>38.00</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.0122</t>
+          <t>0.1601</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2659,12 +2663,12 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>495.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>960.60฿</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -2675,7 +2679,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>82730128600#2</t>
+          <t>113282578128</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2691,12 +2695,12 @@
       <c r="E33" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18678-6-20</t>
+ รถ lot18683-3</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>30/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2711,12 +2715,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>27.60</t>
+          <t>27.50</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.0095</t>
+          <t>0.1566</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2726,15 +2730,19 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>414.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
+          <t>939.60฿</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>压条取出器 一票两件破损件</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2742,7 +2750,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>82730128600</t>
+          <t>82730128600#3</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2758,7 +2766,7 @@
       <c r="E34" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18678-6-19</t>
+ รถ lot18678-6-21</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2778,12 +2786,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>28.10</t>
+          <t>33.00</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.0118</t>
+          <t>0.0122</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2793,7 +2801,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>421.50฿</t>
+          <t>495.00฿</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2801,11 +2809,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>五金配件/3件</t>
-        </is>
-      </c>
+      <c r="N34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2813,7 +2817,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>113278387839#3</t>
+          <t>82730128600#2</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2823,38 +2827,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>UN-INV260903-00023</t>
+          <t>UN-INV260907-00015</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18663-8-3</t>
+ รถ lot18678-6-20</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>30/08/2026</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>25.30</t>
+          <t>27.60</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.0404</t>
+          <t>0.0095</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2864,7 +2868,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>379.50฿</t>
+          <t>414.00฿</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2880,7 +2884,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>113278387839#2</t>
+          <t>82730128600</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2890,38 +2894,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>UN-INV260903-00023</t>
+          <t>UN-INV260907-00015</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18663-8-2</t>
+ รถ lot18678-6-19</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>30/08/2026</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>26.10</t>
+          <t>28.10</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.0304</t>
+          <t>0.0118</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2931,7 +2935,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>391.50฿</t>
+          <t>421.50฿</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2939,7 +2943,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>五金配件/3件</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2947,7 +2955,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>113278387839</t>
+          <t>113278387839#3</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2963,7 +2971,7 @@
       <c r="E37" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18663-8-1</t>
+ รถ lot18663-8-3</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2983,12 +2991,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>25.30</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.0144</t>
+          <t>0.0404</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2998,7 +3006,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>136.50฿</t>
+          <t>379.50฿</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3006,11 +3014,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>配件/3件</t>
-        </is>
-      </c>
+      <c r="N37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -3018,7 +3022,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>113276098937#3</t>
+          <t>113278387839#2</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3028,38 +3032,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>UN-INV260901-00057</t>
+          <t>UN-INV260903-00023</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-45</t>
+ รถ lot18663-8-2</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>17.80</t>
+          <t>26.10</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.0302</t>
+          <t>0.0304</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3069,7 +3073,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>267.00฿</t>
+          <t>391.50฿</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3085,7 +3089,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>113276098937#2</t>
+          <t>113278387839</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3095,38 +3099,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>UN-INV260901-00057</t>
+          <t>UN-INV260903-00023</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-44</t>
+ รถ lot18663-8-1</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>10.90</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.0313</t>
+          <t>0.0144</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -3136,15 +3140,19 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>136.50฿</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>187.80฿</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>配件/3件</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -3152,7 +3160,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>113276098937</t>
+          <t>113276098937#3</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3168,7 +3176,7 @@
       <c r="E40" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-43</t>
+ รถ lot18655-9-45</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -3188,12 +3196,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>33.60</t>
+          <t>17.80</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.0825</t>
+          <t>0.0302</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -3203,7 +3211,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>504.00฿</t>
+          <t>267.00฿</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3211,11 +3219,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>补胎胶片+配件/3件</t>
-        </is>
-      </c>
+      <c r="N40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -3223,7 +3227,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ZY202464580877#4</t>
+          <t>113276098937#2</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3239,7 +3243,7 @@
       <c r="E41" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-17</t>
+ รถ lot18655-9-44</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3259,12 +3263,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>20.10</t>
+          <t>10.90</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.0466</t>
+          <t>0.0313</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -3274,12 +3278,12 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>301.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>187.80฿</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -3290,7 +3294,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ZY202464580877#7</t>
+          <t>113276098937</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3306,7 +3310,7 @@
       <c r="E42" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-16</t>
+ รถ lot18655-9-43</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3326,12 +3330,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>16.60</t>
+          <t>33.60</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.0430</t>
+          <t>0.0825</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3341,15 +3345,19 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>504.00฿</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>258.00฿</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>补胎胶片+配件/3件</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -3357,7 +3365,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ZY202464580877#2</t>
+          <t>ZY202464580877#4</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3373,7 +3381,7 @@
       <c r="E43" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-15</t>
+ รถ lot18655-9-17</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3393,12 +3401,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>25.10</t>
+          <t>20.10</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.0483</t>
+          <t>0.0466</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3408,7 +3416,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>376.50฿</t>
+          <t>301.50฿</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3424,7 +3432,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ZY202464580877#8</t>
+          <t>ZY202464580877#7</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3440,7 +3448,7 @@
       <c r="E44" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-14</t>
+ รถ lot18655-9-16</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3460,12 +3468,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>28.90</t>
+          <t>16.60</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.0800</t>
+          <t>0.0430</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3480,7 +3488,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>480.00฿</t>
+          <t>258.00฿</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -3491,7 +3499,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ZY202464580877#6</t>
+          <t>ZY202464580877#2</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3507,7 +3515,7 @@
       <c r="E45" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-13</t>
+ รถ lot18655-9-15</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -3527,12 +3535,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>20.90</t>
+          <t>25.10</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.0534</t>
+          <t>0.0483</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3542,12 +3550,12 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>376.50฿</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>320.40฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -3558,7 +3566,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ZY202464580877#5</t>
+          <t>ZY202464580877#8</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3574,7 +3582,7 @@
       <c r="E46" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-12</t>
+ รถ lot18655-9-14</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3594,12 +3602,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>26.20</t>
+          <t>28.90</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.0535</t>
+          <t>0.0800</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3609,12 +3617,12 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>393.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>480.00฿</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
@@ -3625,7 +3633,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ZY202464580877</t>
+          <t>ZY202464580877#6</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3641,7 +3649,7 @@
       <c r="E47" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-11</t>
+ รถ lot18655-9-13</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3661,12 +3669,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>20.70</t>
+          <t>20.90</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>0.0531</t>
+          <t>0.0534</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3681,7 +3689,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>318.60฿</t>
+          <t>320.40฿</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -3692,7 +3700,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ZY202464580877#9</t>
+          <t>ZY202464580877#5</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3708,7 +3716,7 @@
       <c r="E48" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-10</t>
+ รถ lot18655-9-12</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3728,12 +3736,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>27.70</t>
+          <t>26.20</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>0.0800</t>
+          <t>0.0535</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3743,12 +3751,12 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>393.00฿</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>480.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -3759,7 +3767,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ZY202464580877#3</t>
+          <t>ZY202464580877</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3775,7 +3783,7 @@
       <c r="E49" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18655-9-9</t>
+ รถ lot18655-9-11</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3795,12 +3803,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>27.10</t>
+          <t>20.70</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.0567</t>
+          <t>0.0531</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3810,19 +3818,15 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>406.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>补胎胶片/9件</t>
-        </is>
-      </c>
+          <t>318.60฿</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -3830,7 +3834,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>S71090288685</t>
+          <t>ZY202464580877#9</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3840,38 +3844,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>UN-INV260831-00017</t>
+          <t>UN-INV260901-00057</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18634-7-3</t>
+ รถ lot18655-9-10</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>29/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>12.10</t>
+          <t>27.70</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0.0240</t>
+          <t>0.0800</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3881,19 +3885,15 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>181.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>配件</t>
-        </is>
-      </c>
+          <t>480.00฿</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -3901,7 +3901,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>YT7638092409979</t>
+          <t>ZY202464580877#3</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3911,38 +3911,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>UN-INV260822-00010</t>
+          <t>UN-INV260901-00057</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18569-7-7</t>
+ รถ lot18655-9-9</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>27.10</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>0.0140</t>
+          <t>0.0567</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3952,7 +3952,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>225.00฿</t>
+          <t>406.50฿</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -3962,7 +3962,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>补胎胶片/9件</t>
         </is>
       </c>
     </row>
@@ -3972,7 +3972,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>435308000517585</t>
+          <t>S71090288685</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3982,38 +3982,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>UN-INV260822-00010</t>
+          <t>UN-INV260831-00017</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18550-6-11</t>
+ รถ lot18634-7-3</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>29/08/2026</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>12.10</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>0.0032</t>
+          <t>0.0240</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -4023,7 +4023,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>54.00฿</t>
+          <t>181.50฿</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -4033,7 +4033,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>气门嘴</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -4043,7 +4043,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>710094401487</t>
+          <t>YT7638092409979</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4059,52 +4059,52 @@
       <c r="E53" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18544-8-14</t>
+ รถ lot18569-7-7</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>107.10</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>0.4536</t>
+          <t>0.0140</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>225.00฿</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2,721.60฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>空的高压充气罐/一票10件，仓库实收到9件，已确认收到的9件先发</t>
+          <t>配件</t>
         </is>
       </c>
     </row>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>773435675083665</t>
+          <t>435308000517585</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4124,38 +4124,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>UN-INV260815-00046</t>
+          <t>UN-INV260822-00010</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18526-6-17</t>
+ รถ lot18550-6-11</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>13.10</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>0.0214</t>
+          <t>0.0032</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -4165,7 +4165,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>196.50฿</t>
+          <t>54.00฿</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -4175,7 +4175,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>补胎工具</t>
+          <t>气门嘴</t>
         </is>
       </c>
     </row>
@@ -4185,7 +4185,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>YT7637032206975</t>
+          <t>710094401487</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4195,43 +4195,43 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>UN-INV260819-00010</t>
+          <t>UN-INV260822-00010</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>มอก.
- รถ lot18523-6-30</t>
+          <t>ธรรมดา
+ รถ lot18544-8-14</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>107.10</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>0.0316</t>
+          <t>0.4536</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>214.88฿</t>
+          <t>2,721.60฿</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>气动模具研磨机+配件</t>
+          <t>空的高压充气罐/一票10件，仓库实收到9件，已确认收到的9件先发</t>
         </is>
       </c>
     </row>
@@ -4256,7 +4256,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ZY202466648481#5</t>
+          <t>773435675083665</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4272,32 +4272,32 @@
       <c r="E56" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18519-6-17</t>
+ รถ lot18526-6-17</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>16.10</t>
+          <t>13.10</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>0.0493</t>
+          <t>0.0214</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -4307,15 +4307,19 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>196.50฿</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>295.80฿</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>补胎工具</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -4323,7 +4327,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ZY202466648481#4</t>
+          <t>YT7637032206975</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4333,13 +4337,13 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>UN-INV260815-00046</t>
+          <t>UN-INV260819-00010</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>ธรรมดา
- รถ lot18519-6-16</t>
+          <t>มอก.
+ รถ lot18523-6-30</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -4354,17 +4358,17 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>20.50</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>0.0656</t>
+          <t>0.0316</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -4379,10 +4383,14 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>393.60฿</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
+          <t>214.88฿</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>气动模具研磨机+配件</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -4390,7 +4398,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ZY202466648481#3</t>
+          <t>ZY202466648481#5</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4406,7 +4414,7 @@
       <c r="E58" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18519-6-15</t>
+ รถ lot18519-6-17</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -4426,12 +4434,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>15.70</t>
+          <t>16.10</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>0.0508</t>
+          <t>0.0493</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4446,7 +4454,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>304.80฿</t>
+          <t>295.80฿</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -4457,7 +4465,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ZY202466648481#2</t>
+          <t>ZY202466648481#4</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4473,7 +4481,7 @@
       <c r="E59" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18519-6-14</t>
+ รถ lot18519-6-16</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -4493,12 +4501,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>20.20</t>
+          <t>20.50</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>0.0660</t>
+          <t>0.0656</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4513,7 +4521,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>396.00฿</t>
+          <t>393.60฿</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -4524,7 +4532,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ZY202466648481</t>
+          <t>ZY202466648481#3</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4540,7 +4548,7 @@
       <c r="E60" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18519-6-13</t>
+ รถ lot18519-6-15</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -4560,12 +4568,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>15.80</t>
+          <t>15.70</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>0.0522</t>
+          <t>0.0508</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4580,14 +4588,10 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>313.20฿</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>补胎胶条/5件</t>
-        </is>
-      </c>
+          <t>304.80฿</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -4595,7 +4599,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>113204676267#2</t>
+          <t>ZY202466648481#2</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4611,32 +4615,32 @@
       <c r="E61" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18518-5-3</t>
+ รถ lot18519-6-14</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>15/08/2026</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>24.60</t>
+          <t>20.20</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>0.0608</t>
+          <t>0.0660</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4646,12 +4650,12 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>369.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>396.00฿</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -4662,7 +4666,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>113204676267</t>
+          <t>ZY202466648481</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4678,32 +4682,32 @@
       <c r="E62" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18518-5-2</t>
+ รถ lot18519-6-13</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>15/08/2026</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>25.00</t>
+          <t>15.80</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>0.0566</t>
+          <t>0.0522</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4713,17 +4717,17 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>375.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>313.20฿</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>真空胎冷补胶片</t>
+          <t>补胎胶条/5件</t>
         </is>
       </c>
     </row>
@@ -4733,7 +4737,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>910061892464#2</t>
+          <t>113204676267#2</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4749,32 +4753,32 @@
       <c r="E63" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18505-5-23</t>
+ รถ lot18518-5-3</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>30.40</t>
+          <t>24.60</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>0.0523</t>
+          <t>0.0608</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -4784,7 +4788,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>456.00฿</t>
+          <t>369.00฿</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -4800,7 +4804,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>910061892464</t>
+          <t>113204676267</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4816,32 +4820,32 @@
       <c r="E64" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18505-5-22</t>
+ รถ lot18518-5-2</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>15.90</t>
+          <t>25.00</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>0.0353</t>
+          <t>0.0566</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4851,7 +4855,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>238.50฿</t>
+          <t>375.00฿</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -4861,7 +4865,7 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>记号蜡笔</t>
+          <t>真空胎冷补胶片</t>
         </is>
       </c>
     </row>
@@ -4871,7 +4875,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>773434709817985</t>
+          <t>910061892464#2</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4881,38 +4885,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>UN-INV260819-00010</t>
+          <t>UN-INV260815-00046</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18535-8</t>
+ รถ lot18505-5-23</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>30.40</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>0.0184</t>
+          <t>0.0523</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4922,19 +4926,15 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>456.00฿</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>110.40฿</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>锅具 二次包装货物变形</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -4942,7 +4942,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>435295775627304</t>
+          <t>910061892464</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4952,38 +4952,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>UN-INV260811-00012</t>
+          <t>UN-INV260815-00046</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18492-2</t>
+ รถ lot18505-5-22</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>5.30</t>
+          <t>15.90</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>0.0090</t>
+          <t>0.0353</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -4993,7 +4993,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>79.50฿</t>
+          <t>238.50฿</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>配件 破损件</t>
+          <t>记号蜡笔</t>
         </is>
       </c>
     </row>
@@ -5013,7 +5013,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>YT7636332367470</t>
+          <t>773434709817985</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -5023,38 +5023,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>UN-INV260811-00012</t>
+          <t>UN-INV260819-00010</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18487-2-27</t>
+ รถ lot18535-8</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>0.0004</t>
+          <t>0.0184</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -5069,12 +5069,12 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>10.00฿</t>
+          <t>110.40฿</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>立牌</t>
+          <t>锅具 二次包装货物变形</t>
         </is>
       </c>
     </row>
@@ -5084,7 +5084,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>S35386280517#2</t>
+          <t>435295775627304</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -5100,32 +5100,32 @@
       <c r="E68" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18475-24</t>
+ รถ lot18492-2</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>8.80</t>
+          <t>5.30</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>0.0045</t>
+          <t>0.0090</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>132.00฿</t>
+          <t>79.50฿</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -5143,7 +5143,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>配件 破损件</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -5151,7 +5155,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>S35386280517</t>
+          <t>YT7636332367470</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -5167,52 +5171,52 @@
       <c r="E69" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18475-23</t>
+ รถ lot18487-2-27</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>103.50</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>0.2236</t>
+          <t>0.0004</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>1,552.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10.00฿</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>气门嘴 顺心捷达，一票16件</t>
+          <t>立牌</t>
         </is>
       </c>
     </row>
@@ -5222,7 +5226,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>YT7635787693833</t>
+          <t>S35386280517#2</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -5238,7 +5242,7 @@
       <c r="E70" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18473-6-41</t>
+ รถ lot18475-24</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -5253,17 +5257,17 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>13.80</t>
+          <t>8.80</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>0.0432</t>
+          <t>0.0045</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -5273,19 +5277,15 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>132.00฿</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>259.20฿</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>气压表/面单没有代码</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -5293,7 +5293,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ZY202465806614</t>
+          <t>S35386280517</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -5303,58 +5303,58 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>UN-INV260807-00009</t>
+          <t>UN-INV260811-00012</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>มอก.
- รถ lot18466-5-51</t>
+          <t>ธรรมดา
+ รถ lot18475-23</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>11.30</t>
+          <t>103.50</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>0.0655</t>
+          <t>0.2236</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1,552.50฿</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>445.40฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>电子数显胎压枪</t>
+          <t>气门嘴 顺心捷达，一票16件</t>
         </is>
       </c>
     </row>
@@ -5364,7 +5364,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>113177184579#7</t>
+          <t>YT7635787693833</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -5374,38 +5374,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>UN-INV260807-00009</t>
+          <t>UN-INV260811-00012</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-17</t>
+ รถ lot18473-6-41</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>9.70</t>
+          <t>13.80</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>0.0305</t>
+          <t>0.0432</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -5420,10 +5420,14 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>183.00฿</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr"/>
+          <t>259.20฿</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>气压表/面单没有代码</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -5431,7 +5435,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>113177184579#5</t>
+          <t>ZY202465806614</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -5446,18 +5450,18 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>ธรรมดา
- รถ lot18463-16</t>
+          <t>มอก.
+ รถ lot18466-5-51</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5467,12 +5471,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>11.30</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>0.0137</t>
+          <t>0.0655</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -5482,15 +5486,19 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>225.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr"/>
+          <t>445.40฿</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>电子数显胎压枪</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -5498,7 +5506,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>113177184579#4</t>
+          <t>113177184579#7</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5514,7 +5522,7 @@
       <c r="E74" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-15</t>
+ รถ lot18463-17</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -5534,12 +5542,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>7.30</t>
+          <t>9.70</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>0.0235</t>
+          <t>0.0305</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -5554,7 +5562,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>141.00฿</t>
+          <t>183.00฿</t>
         </is>
       </c>
       <c r="N74" t="inlineStr"/>
@@ -5565,7 +5573,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>113177184579#3</t>
+          <t>113177184579#5</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5581,7 +5589,7 @@
       <c r="E75" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-14</t>
+ รถ lot18463-16</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -5601,12 +5609,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>11.90</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>0.0302</t>
+          <t>0.0137</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -5616,12 +5624,12 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>225.00฿</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>181.20฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N75" t="inlineStr"/>
@@ -5632,7 +5640,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>113177184579#6</t>
+          <t>113177184579#4</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5648,7 +5656,7 @@
       <c r="E76" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-13</t>
+ รถ lot18463-15</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -5668,12 +5676,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>26.10</t>
+          <t>7.30</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>0.0673</t>
+          <t>0.0235</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -5688,7 +5696,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>403.80฿</t>
+          <t>141.00฿</t>
         </is>
       </c>
       <c r="N76" t="inlineStr"/>
@@ -5699,7 +5707,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>435289604798626</t>
+          <t>113177184579#3</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5715,7 +5723,7 @@
       <c r="E77" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18462-6-6</t>
+ รถ lot18463-14</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -5725,7 +5733,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5735,12 +5743,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>11.90</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>0.0090</t>
+          <t>0.0302</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5750,19 +5758,15 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>144.00฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr">
-        <is>
-          <t>螺丝配件</t>
-        </is>
-      </c>
+          <t>181.20฿</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -5770,7 +5774,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>113177184579#2</t>
+          <t>113177184579#6</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5786,7 +5790,7 @@
       <c r="E78" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-12</t>
+ รถ lot18463-13</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -5806,12 +5810,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>5.30</t>
+          <t>26.10</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>0.0635</t>
+          <t>0.0673</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -5826,7 +5830,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>381.00฿</t>
+          <t>403.80฿</t>
         </is>
       </c>
       <c r="N78" t="inlineStr"/>
@@ -5837,7 +5841,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>113177184579</t>
+          <t>435289604798626</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5853,7 +5857,7 @@
       <c r="E79" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-11</t>
+ รถ lot18462-6-6</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -5863,7 +5867,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5873,12 +5877,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>13.30</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>0.1176</t>
+          <t>0.0090</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -5888,17 +5892,17 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>144.00฿</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>705.60฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>蘑菇钉补胎贴</t>
+          <t>螺丝配件</t>
         </is>
       </c>
     </row>
@@ -5908,7 +5912,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>435289604798722</t>
+          <t>113177184579#2</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5924,7 +5928,7 @@
       <c r="E80" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18462-3</t>
+ รถ lot18463-12</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -5934,7 +5938,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5944,12 +5948,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>5.30</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>0.0029</t>
+          <t>0.0635</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -5959,19 +5963,15 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>64.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr">
-        <is>
-          <t>气门嘴</t>
-        </is>
-      </c>
+          <t>381.00฿</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -5979,7 +5979,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ZY202471573119#2</t>
+          <t>113177184579</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5995,7 +5995,7 @@
       <c r="E81" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-6</t>
+ รถ lot18463-11</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>8.70</t>
+          <t>13.30</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>0.0441</t>
+          <t>0.1176</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -6035,10 +6035,14 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>264.60฿</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
+          <t>705.60฿</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>蘑菇钉补胎贴</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -6046,7 +6050,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>ZY202471573119</t>
+          <t>435289604798722</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -6062,7 +6066,7 @@
       <c r="E82" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18463-5</t>
+ รถ lot18462-3</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -6072,7 +6076,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -6082,12 +6086,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>11.90</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>0.0832</t>
+          <t>0.0029</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -6097,17 +6101,17 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>64.50฿</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>499.20฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>蘑菇钉补胎</t>
+          <t>气门嘴</t>
         </is>
       </c>
     </row>
@@ -6117,7 +6121,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>YT7635427281240</t>
+          <t>ZY202471573119#2</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -6133,7 +6137,7 @@
       <c r="E83" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18458-21</t>
+ รถ lot18463-6</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -6153,12 +6157,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>8.70</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>0.0117</t>
+          <t>0.0441</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -6173,14 +6177,10 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>70.20฿</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr">
-        <is>
-          <t>气阀</t>
-        </is>
-      </c>
+          <t>264.60฿</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -6188,7 +6188,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>79021262374216</t>
+          <t>ZY202471573119</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -6198,38 +6198,38 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>UN-INV260804-00019</t>
+          <t>UN-INV260807-00009</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18435-5-73</t>
+ รถ lot18463-5</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>12.20</t>
+          <t>11.90</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>0.0352</t>
+          <t>0.0832</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>211.20฿</t>
+          <t>499.20฿</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>加长弯头</t>
+          <t>蘑菇钉补胎</t>
         </is>
       </c>
     </row>
@@ -6259,7 +6259,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>113162219964#3</t>
+          <t>YT7635427281240</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -6269,38 +6269,38 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>UN-INV260804-00019</t>
+          <t>UN-INV260807-00009</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18434-9-28</t>
+ รถ lot18458-21</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>18.70</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>0.0443</t>
+          <t>0.0117</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -6310,15 +6310,19 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>280.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr"/>
+          <t>70.20฿</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>气阀</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -6326,7 +6330,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>113162219964#2</t>
+          <t>79021262374216</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -6342,17 +6346,17 @@
       <c r="E86" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18434-9-27</t>
+ รถ lot18435-5-73</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -6362,12 +6366,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>22.90</t>
+          <t>12.20</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>0.0522</t>
+          <t>0.0352</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -6377,15 +6381,19 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>343.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr"/>
+          <t>211.20฿</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>加长弯头</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -6393,7 +6401,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>113162219964</t>
+          <t>113162219964#3</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -6409,7 +6417,7 @@
       <c r="E87" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18434-9-26</t>
+ รถ lot18434-9-28</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -6429,12 +6437,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>25.60</t>
+          <t>18.70</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>0.0574</t>
+          <t>0.0443</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -6444,7 +6452,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>384.00฿</t>
+          <t>280.50฿</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -6452,11 +6460,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N87" t="inlineStr">
-        <is>
-          <t>补胎胶片/3件</t>
-        </is>
-      </c>
+      <c r="N87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -6464,7 +6468,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>113158800045#2</t>
+          <t>113162219964#2</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -6480,32 +6484,32 @@
       <c r="E88" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18427-7-3</t>
+ รถ lot18434-9-27</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>26/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>26/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>26.30</t>
+          <t>22.90</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>0.0377</t>
+          <t>0.0522</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -6515,7 +6519,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>394.50฿</t>
+          <t>343.50฿</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -6531,7 +6535,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>113158800045</t>
+          <t>113162219964</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -6547,32 +6551,32 @@
       <c r="E89" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18427-7-2</t>
+ รถ lot18434-9-26</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>26/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>26/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>26.50</t>
+          <t>25.60</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>0.0379</t>
+          <t>0.0574</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -6582,7 +6586,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>397.50฿</t>
+          <t>384.00฿</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -6592,7 +6596,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>塑料配件/2件</t>
+          <t>补胎胶片/3件</t>
         </is>
       </c>
     </row>
@@ -6602,7 +6606,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>YT2550516723148</t>
+          <t>113158800045#2</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -6618,32 +6622,32 @@
       <c r="E90" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18398-3-10</t>
+ รถ lot18427-7-3</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>26/07/2026</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>26/07/2026</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>26.30</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>0.0127</t>
+          <t>0.0377</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -6653,19 +6657,15 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>394.50฿</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>76.20฿</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr">
-        <is>
-          <t>硅胶风管</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -6673,7 +6673,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>ZY202467269952#4</t>
+          <t>113158800045</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6683,38 +6683,38 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>UN-INV260724-00013</t>
+          <t>UN-INV260804-00019</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18314-8-30</t>
+ รถ lot18427-7-2</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>11/07/2026</t>
+          <t>26/07/2026</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>12/07/2026</t>
+          <t>26/07/2026</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>15.50</t>
+          <t>26.50</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>0.0492</t>
+          <t>0.0379</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -6724,15 +6724,19 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>397.50฿</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>295.20฿</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>塑料配件/2件</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -6740,7 +6744,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>ZY202467269952#3</t>
+          <t>YT2550516723148</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6750,38 +6754,38 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>UN-INV260724-00013</t>
+          <t>UN-INV260804-00019</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18314-8-29</t>
+ รถ lot18398-3-10</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>11/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>12/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>12.50</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>0.0300</t>
+          <t>0.0127</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -6791,15 +6795,19 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>187.50฿</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr"/>
+          <t>76.20฿</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>硅胶风管</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -6807,7 +6815,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>ZY202467269952#2</t>
+          <t>ZY202467269952#4</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6823,7 +6831,7 @@
       <c r="E93" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18314-8-28</t>
+ รถ lot18314-8-30</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -6848,7 +6856,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>0.0508</t>
+          <t>0.0492</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -6863,7 +6871,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>304.80฿</t>
+          <t>295.20฿</t>
         </is>
       </c>
       <c r="N93" t="inlineStr"/>
@@ -6874,7 +6882,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>ZY202467269952</t>
+          <t>ZY202467269952#3</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6890,7 +6898,7 @@
       <c r="E94" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18314-8-27</t>
+ รถ lot18314-8-29</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -6910,12 +6918,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>10.50</t>
+          <t>12.50</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>0.0355</t>
+          <t>0.0300</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -6925,19 +6933,15 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>187.50฿</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>213.00฿</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr">
-        <is>
-          <t>补胎胶片/4件</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -6945,7 +6949,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>773431041004504</t>
+          <t>ZY202467269952#2</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6961,7 +6965,7 @@
       <c r="E95" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18314-5-13</t>
+ รถ lot18314-8-28</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -6981,12 +6985,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>15.50</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>0.0044</t>
+          <t>0.0508</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -7001,14 +7005,10 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>26.40฿</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr">
-        <is>
-          <t>门底条</t>
-        </is>
-      </c>
+          <t>304.80฿</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -7016,7 +7016,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>ZY202467269844#2</t>
+          <t>ZY202467269952</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -7026,38 +7026,38 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>UN-INV260717-00013</t>
+          <t>UN-INV260724-00013</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18288-8-41</t>
+ รถ lot18314-8-27</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>11/07/2026</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>12/07/2026</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>21.00</t>
+          <t>10.50</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>0.0660</t>
+          <t>0.0355</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -7072,10 +7072,14 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>396.00฿</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
+          <t>213.00฿</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>补胎胶片/4件</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -7083,7 +7087,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>ZY202467269844#5</t>
+          <t>773431041004504</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -7093,38 +7097,38 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>UN-INV260717-00013</t>
+          <t>UN-INV260724-00013</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18288-8-40</t>
+ รถ lot18314-5-13</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>11/07/2026</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>12/07/2026</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>27.90</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>0.0800</t>
+          <t>0.0044</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -7139,10 +7143,14 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>480.00฿</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
+          <t>26.40฿</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>门底条</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -7150,7 +7158,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ZY202467269844#3</t>
+          <t>ZY202467269844#2</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -7166,7 +7174,7 @@
       <c r="E98" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18288-8-39</t>
+ รถ lot18288-8-41</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -7186,12 +7194,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>15.60</t>
+          <t>21.00</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>0.0496</t>
+          <t>0.0660</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -7206,7 +7214,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>297.60฿</t>
+          <t>396.00฿</t>
         </is>
       </c>
       <c r="N98" t="inlineStr"/>
@@ -7217,7 +7225,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ZY202467269844#4</t>
+          <t>ZY202467269844#5</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -7233,7 +7241,7 @@
       <c r="E99" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18288-8-38</t>
+ รถ lot18288-8-40</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -7253,12 +7261,12 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>16.00</t>
+          <t>27.90</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>0.0504</t>
+          <t>0.0800</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -7273,7 +7281,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>302.40฿</t>
+          <t>480.00฿</t>
         </is>
       </c>
       <c r="N99" t="inlineStr"/>
@@ -7284,7 +7292,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>ZY202467269844#6</t>
+          <t>ZY202467269844#3</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -7300,7 +7308,7 @@
       <c r="E100" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18288-8-37</t>
+ รถ lot18288-8-39</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -7320,12 +7328,12 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>29.00</t>
+          <t>15.60</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>0.0816</t>
+          <t>0.0496</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -7340,7 +7348,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>489.60฿</t>
+          <t>297.60฿</t>
         </is>
       </c>
       <c r="N100" t="inlineStr"/>
@@ -7351,7 +7359,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>ZY202467269844#7</t>
+          <t>ZY202467269844#4</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -7367,7 +7375,7 @@
       <c r="E101" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18288-8-36</t>
+ รถ lot18288-8-38</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -7387,12 +7395,12 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>15.80</t>
+          <t>16.00</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>0.0519</t>
+          <t>0.0504</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -7407,14 +7415,10 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>311.40฿</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr">
-        <is>
-          <t>补胎胶片/一票7件，已确认6件发陆运1件发海运</t>
-        </is>
-      </c>
+          <t>302.40฿</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cargo_packages_p1-5.xlsx
+++ b/cargo_packages_p1-5.xlsx
@@ -532,7 +532,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -603,7 +603,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -664,12 +664,12 @@
       <c r="E4" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ -</t>
+ รถ lot18761-8-57</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -684,12 +684,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5.80</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.0070</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>87.00฿</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -707,7 +707,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>配件</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">

--- a/cargo_packages_p1-5.xlsx
+++ b/cargo_packages_p1-5.xlsx
@@ -664,7 +664,7 @@
       <c r="E4" t="inlineStr">
         <is>
           <t>ธรรมดา
- รถ lot18761-8-57</t>
+ รถ lot18769-3-57</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>UN-INV260911-00013</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>UN-INV260911-00013</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>UN-INV260911-00013</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">

--- a/cargo_packages_p1-5.xlsx
+++ b/cargo_packages_p1-5.xlsx
@@ -1673,7 +1673,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2087,7 +2087,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">

--- a/cargo_packages_p1-5.xlsx
+++ b/cargo_packages_p1-5.xlsx
@@ -1652,7 +1652,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>UN-INV260912-00011</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>UN-INV260912-00011</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>UN-INV260912-00011</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1857,7 +1857,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>UN-INV260912-00011</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>UN-INV260912-00011</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1995,7 +1995,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>UN-INV260912-00011</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>UN-INV260912-00011</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2133,7 +2133,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>UN-INV260912-00011</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">

--- a/cargo_packages_p1-5.xlsx
+++ b/cargo_packages_p1-5.xlsx
@@ -1105,7 +1105,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12/09/2026</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12/09/2026</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12/09/2026</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12/09/2026</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12/09/2026</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12/09/2026</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
